--- a/labs/lab-05-built-in-skills-visual-and-finance/data/BrightPath_HR_Outsourcing_Finance.xlsx
+++ b/labs/lab-05-built-in-skills-visual-and-finance/data/BrightPath_HR_Outsourcing_Finance.xlsx
@@ -553,7 +553,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>tblClientMonths</t>
@@ -570,7 +570,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>tblClients</t>
@@ -604,7 +604,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>Headcount_Budget</t>
@@ -621,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>Definitions</t>
